--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:12:31+00:00</t>
+    <t>2026-03-18T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:24:59+00:00</t>
+    <t>2026-03-31T06:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,6 +113,21 @@
   </si>
   <si>
     <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>C49165</t>
+  </si>
+  <si>
+    <t>C49163</t>
+  </si>
+  <si>
+    <t>C161601</t>
+  </si>
+  <si>
+    <t>C64982</t>
   </si>
 </sst>
 </file>
@@ -421,4 +437,66 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T06:24:20+00:00</t>
+    <t>2026-04-09T04:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T04:48:36+00:00</t>
+    <t>2026-04-15T07:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:47:05+00:00</t>
+    <t>2026-04-15T19:05:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T19:05:31+00:00</t>
+    <t>2026-04-16T05:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onconova-vs-surgical-procedures.xlsx
+++ b/ValueSet-onconova-vs-surgical-procedures.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T05:59:15+00:00</t>
+    <t>2026-04-26T18:09:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
